--- a/tasks/finalpool/wc-customer-gform-excel-notion/groundtruth_workspace/Customer_Insights_Report.xlsx
+++ b/tasks/finalpool/wc-customer-gform-excel-notion/groundtruth_workspace/Customer_Insights_Report.xlsx
@@ -452,16 +452,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>12000</v>
+        <v>35134.01</v>
       </c>
       <c r="D2" t="n">
-        <v>800</v>
+        <v>1673.05</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -471,16 +471,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>6000</v>
+        <v>3808.28</v>
       </c>
       <c r="D3" t="n">
-        <v>300</v>
+        <v>317.36</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -490,16 +490,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>1500</v>
+        <v>475.88</v>
       </c>
       <c r="D4" t="n">
-        <v>100</v>
+        <v>27.99</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,19 +546,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Customer A</t>
+          <t>William Gonzalez</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>a@example.com</t>
+          <t>william.gonzalez@x.dummyjson.com</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1200</v>
+        <v>4586.91</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -569,19 +569,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Customer B</t>
+          <t>Scarlett Wright</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>b@example.com</t>
+          <t>scarlett.wright@x.dummyjson.com</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1100</v>
+        <v>3362.01</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -592,21 +592,182 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Customer C</t>
+          <t>Addison Wright</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c@example.com</t>
+          <t>addison.wright@x.dummyjson.com</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>3069.08</v>
       </c>
       <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ethan Martinez</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ethan.martinez@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3053.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olivia Wilson</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>olivia.wilson@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2942.96</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Charlotte Lopez</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>charlotte.lopez@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2359.28</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sophia Brown</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sophia.brown@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1620.99</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Carter Baker</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>carter.baker@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1482.45</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mason Parker</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>mason.parker@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1413.99</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>VIP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Henry Hill</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>henry.hill@x.dummyjson.com</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1380.71</v>
+      </c>
+      <c r="D11" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
@@ -678,7 +839,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Upsell campaigns</t>
+          <t>Upsell campaigns and personalized recommendations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -688,7 +849,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Convert to VIP</t>
+          <t>Convert to VIP tier</t>
         </is>
       </c>
     </row>
